--- a/src/nodes/HPC/compressor_stage_4_blade_rotor_coordinates_lattice.xlsx
+++ b/src/nodes/HPC/compressor_stage_4_blade_rotor_coordinates_lattice.xlsx
@@ -346,10 +346,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-15.770317161234413</v>
+        <v>-15.779770082541031</v>
       </c>
       <c r="B1">
-        <v>8.6138920234695373</v>
+        <v>8.5965629934328813</v>
       </c>
       <c r="C1">
         <v>194.11826296981104</v>
@@ -357,10 +357,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-14.343082514286824</v>
+        <v>-14.385459238006481</v>
       </c>
       <c r="B2">
-        <v>8.966447715475292</v>
+        <v>8.9018853252347</v>
       </c>
       <c r="C2">
         <v>194.11826296981104</v>
@@ -368,10 +368,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-13.225835563138929</v>
+        <v>-13.280401488695068</v>
       </c>
       <c r="B3">
-        <v>8.8551505476663213</v>
+        <v>8.7733502955506459</v>
       </c>
       <c r="C3">
         <v>194.11826296981104</v>
@@ -379,10 +379,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-12.156943125954488</v>
+        <v>-12.220804846236101</v>
       </c>
       <c r="B4">
-        <v>8.6714976706120623</v>
+        <v>8.576627107485729</v>
       </c>
       <c r="C4">
         <v>194.11826296981104</v>
@@ -390,10 +390,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-11.12183617192011</v>
+        <v>-11.193091512899413</v>
       </c>
       <c r="B5">
-        <v>8.4372895838132642</v>
+        <v>8.332081411728856</v>
       </c>
       <c r="C5">
         <v>194.11826296981104</v>
@@ -401,10 +401,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-10.114560190401246</v>
+        <v>-10.191710838479025</v>
       </c>
       <c r="B6">
-        <v>8.1614363724896286</v>
+        <v>8.0480387560189044</v>
       </c>
       <c r="C6">
         <v>194.11826296981104</v>
@@ -412,10 +412,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-9.1317076292289574</v>
+        <v>-9.213485614261316</v>
       </c>
       <c r="B7">
-        <v>7.84903695779172</v>
+        <v>7.7292647086839015</v>
       </c>
       <c r="C7">
         <v>194.11826296981104</v>
@@ -423,10 +423,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-8.1712664069766188</v>
+        <v>-8.2565390224348256</v>
       </c>
       <c r="B8">
-        <v>7.5031021357497369</v>
+        <v>7.3785743518685809</v>
       </c>
       <c r="C8">
         <v>194.11826296981104</v>
@@ -434,10 +434,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-7.2301060460584408</v>
+        <v>-7.3179523283143535</v>
       </c>
       <c r="B9">
-        <v>7.1283162244847773</v>
+        <v>7.0003455627687652</v>
       </c>
       <c r="C9">
         <v>194.11826296981104</v>
@@ -445,10 +445,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-6.3048494496640481</v>
+        <v>-6.3945770953595</v>
       </c>
       <c r="B10">
-        <v>6.7297325729993638</v>
+        <v>6.5993007536689907</v>
       </c>
       <c r="C10">
         <v>194.11826296981104</v>
@@ -456,10 +456,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-5.3922514402438324</v>
+        <v>-5.4833879964828052</v>
       </c>
       <c r="B11">
-        <v>6.3122071317308475</v>
+        <v>6.1799776821575936</v>
       </c>
       <c r="C11">
         <v>194.11826296981104</v>
@@ -467,10 +467,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-4.4905729344197756</v>
+        <v>-4.5827631725975158</v>
       </c>
       <c r="B12">
-        <v>5.8783421936388569</v>
+        <v>5.7448090119318742</v>
       </c>
       <c r="C12">
         <v>194.11826296981104</v>
@@ -478,10 +478,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-3.6039673062394413</v>
+        <v>-3.6965715271667809</v>
       </c>
       <c r="B13">
-        <v>5.4219228203372936</v>
+        <v>5.2879916858211784</v>
       </c>
       <c r="C13">
         <v>194.11826296981104</v>
@@ -489,10 +489,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-2.7349141978495366</v>
+        <v>-2.8271224745088026</v>
       </c>
       <c r="B14">
-        <v>4.9392385771326213</v>
+        <v>4.806061760243864</v>
       </c>
       <c r="C14">
         <v>194.11826296981104</v>
@@ -500,10 +500,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-1.8733058663677393</v>
+        <v>-1.9649967098120391</v>
       </c>
       <c r="B15">
-        <v>4.4454142754472379</v>
+        <v>4.3131474668422261</v>
       </c>
       <c r="C15">
         <v>194.11826296981104</v>
@@ -511,10 +511,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-1.0098715746238962</v>
+        <v>-1.1015549280012</v>
       </c>
       <c r="B16">
-        <v>3.9543222657235533</v>
+        <v>3.8222070977380742</v>
       </c>
       <c r="C16">
         <v>194.11826296981104</v>
@@ -522,10 +522,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-0.15127599332553357</v>
+        <v>-0.24300654207569469</v>
       </c>
       <c r="B17">
-        <v>3.4559898083680283</v>
+        <v>3.3239270117472985</v>
       </c>
       <c r="C17">
         <v>194.11826296981104</v>
@@ -533,10 +533,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>0.6938709631792872</v>
+        <v>0.6026263576505152</v>
       </c>
       <c r="B18">
-        <v>2.937533381075669</v>
+        <v>2.8062746913456422</v>
       </c>
       <c r="C18">
         <v>194.11826296981104</v>
@@ -544,10 +544,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>1.5251138138580549</v>
+        <v>1.434919689679957</v>
       </c>
       <c r="B19">
-        <v>2.3982714207316209</v>
+        <v>2.2686140469541809</v>
       </c>
       <c r="C19">
         <v>194.11826296981104</v>
@@ -555,10 +555,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>2.3440356860071638</v>
+        <v>2.2553488747193007</v>
       </c>
       <c r="B20">
-        <v>1.8405728540185469</v>
+        <v>1.7131580959803119</v>
       </c>
       <c r="C20">
         <v>194.11826296981104</v>
@@ -566,10 +566,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>3.1522197069229971</v>
+        <v>3.0653893334752045</v>
       </c>
       <c r="B21">
-        <v>1.2668066076191211</v>
+        <v>1.1421198558314374</v>
       </c>
       <c r="C21">
         <v>194.11826296981104</v>
@@ -577,10 +577,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>3.9509667029185551</v>
+        <v>3.8662533523812668</v>
       </c>
       <c r="B22">
-        <v>0.67891918461582956</v>
+        <v>0.55731766277476469</v>
       </c>
       <c r="C22">
         <v>194.11826296981104</v>
@@ -588,10 +588,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>4.7404482963732884</v>
+        <v>4.6581006807788317</v>
       </c>
       <c r="B23">
-        <v>0.07716739369042136</v>
+        <v>-0.041008871483281736</v>
       </c>
       <c r="C23">
         <v>194.11826296981104</v>
@@ -599,10 +599,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>5.5205538086832648</v>
+        <v>5.4408279337361867</v>
       </c>
       <c r="B24">
-        <v>-0.53861438007553986</v>
+        <v>-0.65301481637647241</v>
       </c>
       <c r="C24">
         <v>194.11826296981104</v>
@@ -610,10 +610,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>6.2911725612445419</v>
+        <v>6.2143317263216042</v>
       </c>
       <c r="B25">
-        <v>-1.1685917516004865</v>
+        <v>-1.2788552413385761</v>
       </c>
       <c r="C25">
         <v>194.11826296981104</v>
@@ -621,10 +621,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>7.0521464498548427</v>
+        <v>6.9784643981919814</v>
       </c>
       <c r="B26">
-        <v>-1.8130013015209057</v>
+        <v>-1.9187516255098815</v>
       </c>
       <c r="C26">
         <v>194.11826296981104</v>
@@ -632,10 +632,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>7.8031276679185231</v>
+        <v>7.7329011873586619</v>
       </c>
       <c r="B27">
-        <v>-2.4723634733454976</v>
+        <v>-2.5731910868567627</v>
       </c>
       <c r="C27">
         <v>194.11826296981104</v>
@@ -643,10 +643,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>8.5437209832415864</v>
+        <v>8.477273056421593</v>
       </c>
       <c r="B28">
-        <v>-3.1472696763010086</v>
+        <v>-3.2427271530521065</v>
       </c>
       <c r="C28">
         <v>194.11826296981104</v>
@@ -654,10 +654,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>9.2735311636300377</v>
+        <v>9.2112109679807279</v>
       </c>
       <c r="B29">
-        <v>-3.8383113196141889</v>
+        <v>-3.9279133517688005</v>
       </c>
       <c r="C29">
         <v>194.11826296981104</v>
@@ -665,10 +665,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>9.9923713137751555</v>
+        <v>9.9345399248797452</v>
       </c>
       <c r="B30">
-        <v>-4.54576806575105</v>
+        <v>-4.6290121652611935</v>
       </c>
       <c r="C30">
         <v>194.11826296981104</v>
@@ -676,10 +676,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>10.700887885909246</v>
+        <v>10.647861090937202</v>
       </c>
       <c r="B31">
-        <v>-5.2686725901346412</v>
+        <v>-5.3451218941094476</v>
       </c>
       <c r="C31">
         <v>194.11826296981104</v>
@@ -687,10 +687,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>11.399935669149913</v>
+        <v>11.351969670215416</v>
       </c>
       <c r="B32">
-        <v>-6.005745821427297</v>
+        <v>-6.0750497934751992</v>
       </c>
       <c r="C32">
         <v>194.11826296981104</v>
@@ -698,10 +698,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>12.090369452614731</v>
+        <v>12.047660866776671</v>
       </c>
       <c r="B33">
-        <v>-6.7557086882913264</v>
+        <v>-6.8176031185200685</v>
       </c>
       <c r="C33">
         <v>194.11826296981104</v>
@@ -709,10 +709,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>12.772704266021359</v>
+        <v>12.73541320062477</v>
       </c>
       <c r="B34">
-        <v>-7.5177905214045078</v>
+        <v>-7.5720641260990647</v>
       </c>
       <c r="C34">
         <v>194.11826296981104</v>
@@ -720,10 +720,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>13.446096101487699</v>
+        <v>13.414438455529499</v>
       </c>
       <c r="B35">
-        <v>-8.2932542595064049</v>
+        <v>-8.3396150798407085</v>
       </c>
       <c r="C35">
         <v>194.11826296981104</v>
@@ -731,10 +731,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>14.109361191731724</v>
+        <v>14.083631731202138</v>
       </c>
       <c r="B36">
-        <v>-9.0838712433520215</v>
+        <v>-9.121913245066894</v>
       </c>
       <c r="C36">
         <v>194.11826296981104</v>
@@ -742,10 +742,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>14.761315769471407</v>
+        <v>14.741888127353983</v>
       </c>
       <c r="B37">
-        <v>-9.8914128136963839</v>
+        <v>-9.92061588709953</v>
       </c>
       <c r="C37">
         <v>194.11826296981104</v>
@@ -753,10 +753,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>15.399944716764855</v>
+        <v>15.387327999250127</v>
       </c>
       <c r="B38">
-        <v>-10.71889431028646</v>
+        <v>-10.738542328250764</v>
       </c>
       <c r="C38">
         <v>194.11826296981104</v>
@@ -764,10 +764,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>16.019907513030649</v>
+        <v>16.014972724370857</v>
       </c>
       <c r="B39">
-        <v>-11.574307068837019</v>
+        <v>-11.583160118793693</v>
       </c>
       <c r="C39">
         <v>194.11826296981104</v>
@@ -775,10 +775,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>16.61503228702751</v>
+        <v>16.619068935750288</v>
       </c>
       <c r="B40">
-        <v>-12.466886424054799</v>
+        <v>-12.463098865991679</v>
       </c>
       <c r="C40">
         <v>194.11826296981104</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>17.179147167514156</v>
+        <v>17.193863266422508</v>
       </c>
       <c r="B41">
-        <v>-13.40586771064652</v>
+        <v>-13.386988177108067</v>
       </c>
       <c r="C41">
         <v>194.11826296981104</v>
@@ -797,10 +797,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>17.179147167514156</v>
+        <v>17.193863266422508</v>
       </c>
       <c r="B42">
-        <v>-13.40586771064652</v>
+        <v>-13.386988177108067</v>
       </c>
       <c r="C42">
         <v>194.11826296981104</v>
@@ -808,10 +808,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>16.325106202870547</v>
+        <v>16.348916219063735</v>
       </c>
       <c r="B43">
-        <v>-12.900719911942634</v>
+        <v>-12.868307130986912</v>
       </c>
       <c r="C43">
         <v>194.11826296981104</v>
@@ -819,10 +819,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>15.489847856711007</v>
+        <v>15.521063883512079</v>
       </c>
       <c r="B44">
-        <v>-12.367466574158652</v>
+        <v>-12.323985333971523</v>
       </c>
       <c r="C44">
         <v>194.11826296981104</v>
@@ -830,10 +830,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>14.667273158869472</v>
+        <v>14.704625674000754</v>
       </c>
       <c r="B45">
-        <v>-11.815233945825703</v>
+        <v>-11.762543227133003</v>
       </c>
       <c r="C45">
         <v>194.11826296981104</v>
@@ -841,10 +841,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>13.851283139179857</v>
+        <v>13.893921004762943</v>
       </c>
       <c r="B46">
-        <v>-11.253148275474905</v>
+        <v>-11.192501251542431</v>
       </c>
       <c r="C46">
         <v>194.11826296981104</v>
@@ -852,10 +852,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>13.036607381353944</v>
+        <v>13.084041242294953</v>
       </c>
       <c r="B47">
-        <v>-10.689095997635231</v>
+        <v>-10.621221979340227</v>
       </c>
       <c r="C47">
         <v>194.11826296981104</v>
@@ -863,10 +863,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>12.221289684614868</v>
+        <v>12.273165562145486</v>
       </c>
       <c r="B48">
-        <v>-10.126004290827023</v>
+        <v>-10.05143650694407</v>
       </c>
       <c r="C48">
         <v>194.11826296981104</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>11.40420240206362</v>
+        <v>11.460245092126344</v>
       </c>
       <c r="B49">
-        <v>-9.565560519568459</v>
+        <v>-9.48471806184096</v>
       </c>
       <c r="C49">
         <v>194.11826296981104</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>10.584217886801191</v>
+        <v>10.644230960049336</v>
       </c>
       <c r="B50">
-        <v>-9.00945204837773</v>
+        <v>-8.9226398715179016</v>
       </c>
       <c r="C50">
         <v>194.11826296981104</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>9.7605453446971886</v>
+        <v>9.8243880759330136</v>
       </c>
       <c r="B51">
-        <v>-8.4588621891213531</v>
+        <v>-8.3663045143226356</v>
       </c>
       <c r="C51">
         <v>194.11826296981104</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>8.9337413926956053</v>
+        <v>9.0012364786228609</v>
       </c>
       <c r="B52">
-        <v>-7.9129580430591515</v>
+        <v>-7.8149319720458372</v>
       </c>
       <c r="C52">
         <v>194.11826296981104</v>
@@ -918,10 +918,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>8.104699500509069</v>
+        <v>8.1756099891711251</v>
       </c>
       <c r="B53">
-        <v>-7.3704026587992946</v>
+        <v>-7.26727157733892</v>
       </c>
       <c r="C53">
         <v>194.11826296981104</v>
@@ -929,10 +929,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>7.2743131378501742</v>
+        <v>7.3483424286300236</v>
       </c>
       <c r="B54">
-        <v>-6.8298590849499279</v>
+        <v>-6.7220726628532912</v>
       </c>
       <c r="C54">
         <v>194.11826296981104</v>
@@ -940,10 +940,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>6.4432648000372739</v>
+        <v>6.5200709446361023</v>
       </c>
       <c r="B55">
-        <v>-6.2903060635401413</v>
+        <v>-6.1783795562140433</v>
       </c>
       <c r="C55">
         <v>194.11826296981104</v>
@@ -951,10 +951,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>5.61139308481161</v>
+        <v>5.6906459911630813</v>
       </c>
       <c r="B56">
-        <v>-5.7519851102827113</v>
+        <v>-5.6364165649409577</v>
       </c>
       <c r="C56">
         <v>194.11826296981104</v>
@@ -962,10 +962,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>4.778325615520159</v>
+        <v>4.8597213487689856</v>
       </c>
       <c r="B57">
-        <v>-5.2154534343113355</v>
+        <v>-5.0967029915274988</v>
       </c>
       <c r="C57">
         <v>194.11826296981104</v>
@@ -973,10 +973,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>3.943690015509898</v>
+        <v>4.0269507980118435</v>
       </c>
       <c r="B58">
-        <v>-4.6812682447597131</v>
+        <v>-4.5597581384671271</v>
       </c>
       <c r="C58">
         <v>194.11826296981104</v>
@@ -984,10 +984,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>3.1071588003900263</v>
+        <v>3.1920298656906847</v>
       </c>
       <c r="B59">
-        <v>-4.1499195758236294</v>
+        <v>-4.0260386921075249</v>
       </c>
       <c r="C59">
         <v>194.11826296981104</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>2.26858405481867</v>
+        <v>2.3548210635685787</v>
       </c>
       <c r="B60">
-        <v>-3.6216287619472207</v>
+        <v>-3.4957508742132779</v>
       </c>
       <c r="C60">
         <v>194.11826296981104</v>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>1.4278627557161898</v>
+        <v>1.5152286496496161</v>
       </c>
       <c r="B61">
-        <v>-3.0965499626367134</v>
+        <v>-2.9690382904031982</v>
       </c>
       <c r="C61">
         <v>194.11826296981104</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>0.58489188000293846</v>
+        <v>0.67315688193787526</v>
       </c>
       <c r="B62">
-        <v>-2.5748373373983315</v>
+        <v>-2.4460445462960956</v>
       </c>
       <c r="C62">
         <v>194.11826296981104</v>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-0.26015189713305342</v>
+        <v>-0.17122944572538992</v>
       </c>
       <c r="B63">
-        <v>-2.0562265167350358</v>
+        <v>-1.9265224638242628</v>
       </c>
       <c r="C63">
         <v>194.11826296981104</v>
@@ -1039,10 +1039,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-1.1059731074330548</v>
+        <v>-1.0167233961502431</v>
       </c>
       <c r="B64">
-        <v>-1.5387790151367449</v>
+        <v>-1.40866173017393</v>
       </c>
       <c r="C64">
         <v>194.11826296981104</v>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-1.9509965843706565</v>
+        <v>-1.8618574963095727</v>
       </c>
       <c r="B65">
-        <v>-1.0201378180901162</v>
+        <v>-0.89026124884481206</v>
       </c>
       <c r="C65">
         <v>194.11826296981104</v>
@@ -1061,10 +1061,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-2.79364716141946</v>
+        <v>-2.7051642731762806</v>
       </c>
       <c r="B66">
-        <v>-0.49794591108179947</v>
+        <v>-0.36911992333661725</v>
       </c>
       <c r="C66">
         <v>194.11826296981104</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-3.6343903887736815</v>
+        <v>-3.5470778608521449</v>
       </c>
       <c r="B67">
-        <v>0.027100075693182145</v>
+        <v>0.15411107863959198</v>
       </c>
       <c r="C67">
         <v>194.11826296981104</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-4.4818546835100639</v>
+        <v>-4.3956388219545381</v>
       </c>
       <c r="B68">
-        <v>0.54208893320636742</v>
+        <v>0.6673715325273839</v>
       </c>
       <c r="C68">
         <v>194.11826296981104</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-5.3427262850460311</v>
+        <v>-5.2570781027258926</v>
       </c>
       <c r="B69">
-        <v>1.0370156473323566</v>
+        <v>1.1613154989368433</v>
       </c>
       <c r="C69">
         <v>194.11826296981104</v>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-6.207759855279197</v>
+        <v>-6.1227817553932979</v>
       </c>
       <c r="B70">
-        <v>1.5257145623914343</v>
+        <v>1.6488632359894877</v>
       </c>
       <c r="C70">
         <v>194.11826296981104</v>
@@ -1116,10 +1116,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-7.0668754240900755</v>
+        <v>-6.9833582022394438</v>
       </c>
       <c r="B71">
-        <v>2.0232689317840613</v>
+        <v>2.144101386822121</v>
       </c>
       <c r="C71">
         <v>194.11826296981104</v>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-7.9225860708105769</v>
+        <v>-7.841150239784727</v>
       </c>
       <c r="B72">
-        <v>2.5259182867856929</v>
+        <v>2.6435159371212364</v>
       </c>
       <c r="C72">
         <v>194.11826296981104</v>
@@ -1138,10 +1138,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-8.7790813676685122</v>
+        <v>-8.70006291014946</v>
       </c>
       <c r="B73">
-        <v>3.0273935235396157</v>
+        <v>3.14124962451423</v>
       </c>
       <c r="C73">
         <v>194.11826296981104</v>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-9.6346638090239161</v>
+        <v>-9.558515863615888</v>
       </c>
       <c r="B74">
-        <v>3.5302347197854327</v>
+        <v>3.6396728518424015</v>
       </c>
       <c r="C74">
         <v>194.11826296981104</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-10.486132546805322</v>
+        <v>-10.413528029680764</v>
       </c>
       <c r="B75">
-        <v>4.0392314931495754</v>
+        <v>4.1432569952268654</v>
       </c>
       <c r="C75">
         <v>194.11826296981104</v>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-11.330160441083107</v>
+        <v>-11.262000846537003</v>
       </c>
       <c r="B76">
-        <v>4.5593624392094627</v>
+        <v>4.6566496586940822</v>
       </c>
       <c r="C76">
         <v>194.11826296981104</v>
@@ -1182,10 +1182,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-12.1636699036975</v>
+        <v>-12.1010683819558</v>
       </c>
       <c r="B77">
-        <v>5.0952327345207582</v>
+        <v>5.1841495198226912</v>
       </c>
       <c r="C77">
         <v>194.11826296981104</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-12.984707845426328</v>
+        <v>-12.928912713325325</v>
       </c>
       <c r="B78">
-        <v>5.6497649016011362</v>
+        <v>5.7284833224946965</v>
       </c>
       <c r="C78">
         <v>194.11826296981104</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-13.789928507836535</v>
+        <v>-13.742418324056263</v>
       </c>
       <c r="B79">
-        <v>6.2279653959920696</v>
+        <v>6.2943241016038689</v>
       </c>
       <c r="C79">
         <v>194.11826296981104</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-14.573444858866832</v>
+        <v>-14.536101931556367</v>
       </c>
       <c r="B80">
-        <v>6.8386433307469092</v>
+        <v>6.8898963586578477</v>
       </c>
       <c r="C80">
         <v>194.11826296981104</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-15.320759846481575</v>
+        <v>-15.296457598513696</v>
       </c>
       <c r="B81">
-        <v>7.5034914992788568</v>
+        <v>7.5354579592536517</v>
       </c>
       <c r="C81">
         <v>194.11826296981104</v>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-15.770317161234413</v>
+        <v>-15.779770082541031</v>
       </c>
       <c r="B82">
-        <v>8.6138920234695373</v>
+        <v>8.5965629934328813</v>
       </c>
       <c r="C82">
         <v>194.11826296981104</v>
@@ -1258,10 +1258,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-19.506737321820886</v>
+        <v>-19.442204699430402</v>
       </c>
       <c r="B1">
-        <v>7.13623848417585</v>
+        <v>7.3102241464265934</v>
       </c>
       <c r="C1">
         <v>224.36768702792492</v>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-18.240950076151528</v>
+        <v>-18.221738467452582</v>
       </c>
       <c r="B2">
-        <v>7.191387627147531</v>
+        <v>7.24603906727448</v>
       </c>
       <c r="C2">
         <v>224.36768702792492</v>
@@ -1280,10 +1280,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-17.078212209813859</v>
+        <v>-17.078098467596519</v>
       </c>
       <c r="B3">
-        <v>6.9971086359442749</v>
+        <v>7.0005062767518922</v>
       </c>
       <c r="C3">
         <v>224.36768702792492</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-15.931665541842218</v>
+        <v>-15.947041243131114</v>
       </c>
       <c r="B4">
-        <v>6.7636393029390138</v>
+        <v>6.7252719447536284</v>
       </c>
       <c r="C4">
         <v>224.36768702792492</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-14.796482093267288</v>
+        <v>-14.82499513416683</v>
       </c>
       <c r="B5">
-        <v>6.5026656158976284</v>
+        <v>6.4287669461107662</v>
       </c>
       <c r="C5">
         <v>224.36768702792492</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-13.670693501907762</v>
+        <v>-13.710503572719118</v>
       </c>
       <c r="B6">
-        <v>6.218951940306324</v>
+        <v>6.1144294979941574</v>
       </c>
       <c r="C6">
         <v>224.36768702792492</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-12.553176302609888</v>
+        <v>-12.602734953950375</v>
       </c>
       <c r="B7">
-        <v>5.9152175920787755</v>
+        <v>5.784222597024848</v>
       </c>
       <c r="C7">
         <v>224.36768702792492</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-11.443269989969398</v>
+        <v>-11.501200117947526</v>
       </c>
       <c r="B8">
-        <v>5.5930613060319114</v>
+        <v>5.4393009012965834</v>
       </c>
       <c r="C8">
         <v>224.36768702792492</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-10.339941927280773</v>
+        <v>-10.405134726923034</v>
       </c>
       <c r="B9">
-        <v>5.2549825503663969</v>
+        <v>5.0814686240924658</v>
       </c>
       <c r="C9">
         <v>224.36768702792492</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-9.24207721275035</v>
+        <v>-9.3137136271800784</v>
       </c>
       <c r="B10">
-        <v>4.9036799136228364</v>
+        <v>4.7126735341669015</v>
       </c>
       <c r="C10">
         <v>224.36768702792492</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-8.148604015533131</v>
+        <v>-8.2261435792592277</v>
       </c>
       <c r="B11">
-        <v>4.5417477323178854</v>
+        <v>4.3347880669701926</v>
       </c>
       <c r="C11">
         <v>224.36768702792492</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-7.0589502065794338</v>
+        <v>-7.1420009652507188</v>
       </c>
       <c r="B12">
-        <v>4.1705708287793977</v>
+        <v>3.9488121692172578</v>
       </c>
       <c r="C12">
         <v>224.36768702792492</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-5.974499393072163</v>
+        <v>-6.0623087392061432</v>
       </c>
       <c r="B13">
-        <v>3.7868002206039741</v>
+        <v>3.5523311659856311</v>
       </c>
       <c r="C13">
         <v>224.36768702792492</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-4.8960791117450579</v>
+        <v>-4.9876785999377509</v>
       </c>
       <c r="B14">
-        <v>3.3884328783236453</v>
+        <v>3.1439011470823206</v>
       </c>
       <c r="C14">
         <v>224.36768702792492</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-3.8203368813025969</v>
+        <v>-3.915630653339111</v>
       </c>
       <c r="B15">
-        <v>2.9835833889434005</v>
+        <v>2.7293758828696286</v>
       </c>
       <c r="C15">
         <v>224.36768702792492</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-2.7441978224647703</v>
+        <v>-2.843890353006465</v>
       </c>
       <c r="B16">
-        <v>2.5796944115709581</v>
+        <v>2.314124422086985</v>
       </c>
       <c r="C16">
         <v>224.36768702792492</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-1.6698774820428282</v>
+        <v>-1.7740961362653902</v>
       </c>
       <c r="B17">
-        <v>2.1714032772519571</v>
+        <v>1.8942792464270095</v>
       </c>
       <c r="C17">
         <v>224.36768702792492</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-0.60023688293829069</v>
+        <v>-0.70836388594142685</v>
       </c>
       <c r="B18">
-        <v>1.7517849602483762</v>
+        <v>1.4648458312677963</v>
       </c>
       <c r="C18">
         <v>224.36768702792492</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>0.4645714736774913</v>
+        <v>0.35319371686937029</v>
       </c>
       <c r="B19">
-        <v>1.3204703357496217</v>
+        <v>1.0255581937761558</v>
       </c>
       <c r="C19">
         <v>224.36768702792492</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>1.5250722170657249</v>
+        <v>1.4109647915033308</v>
       </c>
       <c r="B20">
-        <v>0.87872925417695069</v>
+        <v>0.57733248656606873</v>
       </c>
       <c r="C20">
         <v>224.36768702792492</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>2.5817899764876047</v>
+        <v>2.4653374572967723</v>
       </c>
       <c r="B21">
-        <v>0.42783156595162525</v>
+        <v>0.12108486225152326</v>
       </c>
       <c r="C21">
         <v>224.36768702792492</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>3.6351559793323429</v>
+        <v>3.5166307218077466</v>
       </c>
       <c r="B22">
-        <v>-0.031178955118183742</v>
+        <v>-0.34243166435777889</v>
       </c>
       <c r="C22">
         <v>224.36768702792492</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>4.6852278455011627</v>
+        <v>4.5648871454811815</v>
       </c>
       <c r="B23">
-        <v>-0.49816284167664887</v>
+        <v>-0.81311662966925</v>
       </c>
       <c r="C23">
         <v>224.36768702792492</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>5.7319697930233042</v>
+        <v>5.6100801769837405</v>
       </c>
       <c r="B24">
-        <v>-0.97320670298103462</v>
+        <v>-1.2910327078945874</v>
       </c>
       <c r="C24">
         <v>224.36768702792492</v>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>6.7753460399279986</v>
+        <v>6.6521832649820762</v>
       </c>
       <c r="B25">
-        <v>-1.4563971482886011</v>
+        <v>-1.7762425732454834</v>
       </c>
       <c r="C25">
         <v>224.36768702792492</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>7.8153053785298825</v>
+        <v>7.6911584206971062</v>
       </c>
       <c r="B26">
-        <v>-1.9478581243663873</v>
+        <v>-2.2688358979335352</v>
       </c>
       <c r="C26">
         <v>224.36768702792492</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>8.8517348982852511</v>
+        <v>8.7269219055668366</v>
       </c>
       <c r="B27">
-        <v>-2.447862928020561</v>
+        <v>-2.7690103461699684</v>
       </c>
       <c r="C27">
         <v>224.36768702792492</v>
@@ -1555,10 +1555,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>9.88450626293579</v>
+        <v>9.759378543583523</v>
       </c>
       <c r="B28">
-        <v>-2.9567221935670625</v>
+        <v>-3.2769905801659047</v>
       </c>
       <c r="C28">
         <v>224.36768702792492</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>10.913491136223188</v>
+        <v>10.788433158739425</v>
       </c>
       <c r="B29">
-        <v>-3.4747465553218353</v>
+        <v>-3.7930012621324716</v>
       </c>
       <c r="C29">
         <v>224.36768702792492</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>11.938630691244478</v>
+        <v>11.814041957535642</v>
       </c>
       <c r="B30">
-        <v>-4.00207840215457</v>
+        <v>-4.3171457662763428</v>
       </c>
       <c r="C30">
         <v>224.36768702792492</v>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>12.960144138518082</v>
+        <v>12.836366676508661</v>
       </c>
       <c r="B31">
-        <v>-4.5381871411499608</v>
+        <v>-4.8490423147864119</v>
       </c>
       <c r="C31">
         <v>224.36768702792492</v>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>13.978320197917761</v>
+        <v>13.855620434703797</v>
       </c>
       <c r="B32">
-        <v>-5.0823739339464522</v>
+        <v>-5.3881878418471176</v>
       </c>
       <c r="C32">
         <v>224.36768702792492</v>
@@ -1610,10 +1610,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>14.993447589317276</v>
+        <v>14.872016351166376</v>
       </c>
       <c r="B33">
-        <v>-5.6339399421824883</v>
+        <v>-5.9340792816429024</v>
       </c>
       <c r="C33">
         <v>224.36768702792492</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>16.005702601901561</v>
+        <v>15.885684358433904</v>
       </c>
       <c r="B34">
-        <v>-6.1924584628273678</v>
+        <v>-6.4864099294499047</v>
       </c>
       <c r="C34">
         <v>224.36768702792492</v>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>17.014811802100226</v>
+        <v>16.8964216430126</v>
       </c>
       <c r="B35">
-        <v>-6.7585913341737918</v>
+        <v>-7.0456585249110111</v>
       </c>
       <c r="C35">
         <v>224.36768702792492</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>18.020389325654072</v>
+        <v>17.903942204900869</v>
       </c>
       <c r="B36">
-        <v>-7.3332725298453187</v>
+        <v>-7.6125001687608123</v>
       </c>
       <c r="C36">
         <v>224.36768702792492</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>19.022049308303874</v>
+        <v>18.907960044097127</v>
       </c>
       <c r="B37">
-        <v>-7.9174360234655126</v>
+        <v>-8.1876099617338944</v>
       </c>
       <c r="C37">
         <v>224.36768702792492</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>20.019130227686137</v>
+        <v>19.90798524955807</v>
       </c>
       <c r="B38">
-        <v>-8.5126830113726317</v>
+        <v>-8.77214433496093</v>
       </c>
       <c r="C38">
         <v>224.36768702792492</v>
@@ -1676,10 +1676,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>21.009867929020132</v>
+        <v>20.902712266073575</v>
       </c>
       <c r="B39">
-        <v>-9.1232835807637152</v>
+        <v>-9.3691850411569053</v>
       </c>
       <c r="C39">
         <v>224.36768702792492</v>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>21.992222599420867</v>
+        <v>21.890631627391798</v>
       </c>
       <c r="B40">
-        <v>-9.7541750415505177</v>
+        <v>-9.9822951634329</v>
       </c>
       <c r="C40">
         <v>224.36768702792492</v>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>22.964154426003322</v>
+        <v>22.870233867260922</v>
       </c>
       <c r="B41">
-        <v>-10.410294703644782</v>
+        <v>-10.61503778489999</v>
       </c>
       <c r="C41">
         <v>224.36768702792492</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>22.964154426003322</v>
+        <v>22.870233867260922</v>
       </c>
       <c r="B42">
-        <v>-10.410294703644782</v>
+        <v>-10.61503778489999</v>
       </c>
       <c r="C42">
         <v>224.36768702792492</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>21.895960618532225</v>
+        <v>21.819433667603242</v>
       </c>
       <c r="B43">
-        <v>-9.98717446804637</v>
+        <v>-10.150357382616559</v>
       </c>
       <c r="C43">
         <v>224.36768702792492</v>
@@ -1731,10 +1731,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>20.833876201146293</v>
+        <v>20.772544033001623</v>
       </c>
       <c r="B44">
-        <v>-9.5492666249943916</v>
+        <v>-9.6764461225454177</v>
       </c>
       <c r="C44">
         <v>224.36768702792492</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>19.775866791390449</v>
+        <v>19.728061044845905</v>
       </c>
       <c r="B45">
-        <v>-9.1014953401971788</v>
+        <v>-9.1968539926334749</v>
       </c>
       <c r="C45">
         <v>224.36768702792492</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>18.719898006809604</v>
+        <v>18.684480784525938</v>
       </c>
       <c r="B46">
-        <v>-8.6487847793630461</v>
+        <v>-8.7151309808276345</v>
       </c>
       <c r="C46">
         <v>224.36768702792492</v>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>17.664210932485091</v>
+        <v>17.64050304979212</v>
       </c>
       <c r="B47">
-        <v>-8.1953923467498822</v>
+        <v>-8.234346204222069</v>
       </c>
       <c r="C47">
         <v>224.36768702792492</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>16.60814852364383</v>
+        <v>16.595642503837016</v>
       </c>
       <c r="B48">
-        <v>-7.7429084008137909</v>
+        <v>-7.7556452964999725</v>
       </c>
       <c r="C48">
         <v>224.36768702792492</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>15.551329203049153</v>
+        <v>15.549617526213737</v>
       </c>
       <c r="B49">
-        <v>-7.2922565385604354</v>
+        <v>-7.2796930204918029</v>
       </c>
       <c r="C49">
         <v>224.36768702792492</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>14.493371393464386</v>
+        <v>14.502146496475382</v>
       </c>
       <c r="B50">
-        <v>-6.8443603569954794</v>
+        <v>-6.8071541390280119</v>
       </c>
       <c r="C50">
         <v>224.36768702792492</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>13.434005737422194</v>
+        <v>13.453030765210855</v>
       </c>
       <c r="B51">
-        <v>-6.3998718283184806</v>
+        <v>-6.3384975624674169</v>
       </c>
       <c r="C51">
         <v>224.36768702792492</v>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>12.373411756532528</v>
+        <v>12.402403567152144</v>
       </c>
       <c r="B52">
-        <v>-5.9583564255045616</v>
+        <v>-5.8734087912822437</v>
       </c>
       <c r="C52">
         <v>224.36768702792492</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>11.311881192174679</v>
+        <v>11.350481108067026</v>
       </c>
       <c r="B53">
-        <v>-5.519107996722739</v>
+        <v>-5.411377473473074</v>
       </c>
       <c r="C53">
         <v>224.36768702792492</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>10.249705785727933</v>
+        <v>10.297479593723276</v>
       </c>
       <c r="B54">
-        <v>-5.0814203901420241</v>
+        <v>-4.9518932570404948</v>
       </c>
       <c r="C54">
         <v>224.36768702792492</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>9.18710756715106</v>
+        <v>9.2435636409532282</v>
       </c>
       <c r="B55">
-        <v>-4.644756188470752</v>
+        <v>-4.49456756525786</v>
       </c>
       <c r="C55">
         <v>224.36768702792492</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>8.1240297207207988</v>
+        <v>8.1886915108474945</v>
       </c>
       <c r="B56">
-        <v>-4.2092529125745308</v>
+        <v>-4.0394989224896358</v>
       </c>
       <c r="C56">
         <v>224.36768702792492</v>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>7.06034571929337</v>
+        <v>7.1327698755612445</v>
       </c>
       <c r="B57">
-        <v>-3.7752168178582881</v>
+        <v>-3.5869076283730559</v>
       </c>
       <c r="C57">
         <v>224.36768702792492</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>5.9959290357250064</v>
+        <v>6.0757054072496581</v>
       </c>
       <c r="B58">
-        <v>-3.3429541597269523</v>
+        <v>-3.1370139825453611</v>
       </c>
       <c r="C58">
         <v>224.36768702792492</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>4.9306683687634267</v>
+        <v>5.0174160113775166</v>
       </c>
       <c r="B59">
-        <v>-2.9127343397418275</v>
+        <v>-2.6900117685055487</v>
       </c>
       <c r="C59">
         <v>224.36768702792492</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>3.8645133207224185</v>
+        <v>3.9578645266481081</v>
       </c>
       <c r="B60">
-        <v>-2.4846793440897583</v>
+        <v>-2.2459887051996783</v>
       </c>
       <c r="C60">
         <v>224.36768702792492</v>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>2.7974287198072747</v>
+        <v>2.8970250250743392</v>
       </c>
       <c r="B61">
-        <v>-2.0588743051139673</v>
+        <v>-1.8050059954355744</v>
       </c>
       <c r="C61">
         <v>224.36768702792492</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>1.729379394223278</v>
+        <v>1.8348715786691081</v>
       </c>
       <c r="B62">
-        <v>-1.6354043551576747</v>
+        <v>-1.3671248420210582</v>
       </c>
       <c r="C62">
         <v>224.36768702792492</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>0.66042336669543578</v>
+        <v>0.771447159395776</v>
       </c>
       <c r="B63">
-        <v>-1.2141290518414076</v>
+        <v>-0.93224380997757816</v>
       </c>
       <c r="C63">
         <v>224.36768702792492</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-0.40900856197240987</v>
+        <v>-0.29292966098049983</v>
       </c>
       <c r="B64">
-        <v>-0.79400565389489364</v>
+        <v>-0.49961091318106965</v>
       </c>
       <c r="C64">
         <v>224.36768702792492</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-1.4783923964566927</v>
+        <v>-1.357871410744099</v>
       </c>
       <c r="B65">
-        <v>-0.37376584532516588</v>
+        <v>-0.0683115277210963</v>
       </c>
       <c r="C65">
         <v>224.36768702792492</v>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-2.54720414143386</v>
+        <v>-2.422990618179413</v>
       </c>
       <c r="B66">
-        <v>0.047858689860746775</v>
+        <v>0.36256897031278329</v>
       </c>
       <c r="C66">
         <v>224.36768702792492</v>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-3.6155970988154489</v>
+        <v>-3.4884007824060612</v>
       </c>
       <c r="B67">
-        <v>0.47049688868303585</v>
+        <v>0.79276266714921217</v>
       </c>
       <c r="C67">
         <v>224.36768702792492</v>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-4.6864337594534238</v>
+        <v>-4.5562192858846338</v>
       </c>
       <c r="B68">
-        <v>0.88722017227079752</v>
+        <v>1.2172714982896646</v>
       </c>
       <c r="C68">
         <v>224.36768702792492</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-5.7619313789835145</v>
+        <v>-5.6280863116488806</v>
       </c>
       <c r="B69">
-        <v>1.2926617355079355</v>
+        <v>1.6322238246964851</v>
       </c>
       <c r="C69">
         <v>224.36768702792492</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-6.8390170832360848</v>
+        <v>-6.7017293616842206</v>
       </c>
       <c r="B70">
-        <v>1.6942593841886753</v>
+        <v>2.0429838599026726</v>
       </c>
       <c r="C70">
         <v>224.36768702792492</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-7.9143405787328209</v>
+        <v>-7.77467077692382</v>
       </c>
       <c r="B71">
-        <v>2.1001224097678128</v>
+        <v>2.4554000984773188</v>
       </c>
       <c r="C71">
         <v>224.36768702792492</v>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-8.9887320245659836</v>
+        <v>-8.8475249351400951</v>
       </c>
       <c r="B72">
-        <v>2.5082414354320623</v>
+        <v>2.8680223065632098</v>
       </c>
       <c r="C72">
         <v>224.36768702792492</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-10.063577859363658</v>
+        <v>-9.9213176829444247</v>
       </c>
       <c r="B73">
-        <v>2.9152606253443363</v>
+        <v>3.2784289813734251</v>
       </c>
       <c r="C73">
         <v>224.36768702792492</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-11.138309187326613</v>
+        <v>-10.995628705464792</v>
       </c>
       <c r="B74">
-        <v>3.3225569758403948</v>
+        <v>3.68761227282852</v>
       </c>
       <c r="C74">
         <v>224.36768702792492</v>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-12.211857613811173</v>
+        <v>-12.069668273610912</v>
       </c>
       <c r="B75">
-        <v>3.7327165062079044</v>
+        <v>4.097436330180261</v>
       </c>
       <c r="C75">
         <v>224.36768702792492</v>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-13.283112083223227</v>
+        <v>-13.142615162902841</v>
       </c>
       <c r="B76">
-        <v>4.1484284953692878</v>
+        <v>4.5098396472978122</v>
       </c>
       <c r="C76">
         <v>224.36768702792492</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-14.351044014810427</v>
+        <v>-14.213709179050914</v>
       </c>
       <c r="B77">
-        <v>4.5721825942042491</v>
+        <v>4.926616656770415</v>
       </c>
       <c r="C77">
         <v>224.36768702792492</v>
@@ -2105,10 +2105,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-15.414997388137964</v>
+        <v>-15.282465743916216</v>
       </c>
       <c r="B78">
-        <v>5.0055666817868252</v>
+        <v>5.3489112014502371</v>
       </c>
       <c r="C78">
         <v>224.36768702792492</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-16.473853417345875</v>
+        <v>-16.348058032953983</v>
       </c>
       <c r="B79">
-        <v>5.4512887479312448</v>
+        <v>5.7786749941150362</v>
       </c>
       <c r="C79">
         <v>224.36768702792492</v>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-17.525648806103288</v>
+        <v>-17.409034653372668</v>
       </c>
       <c r="B80">
-        <v>5.9141008963747579</v>
+        <v>6.2193340359336382</v>
       </c>
       <c r="C80">
         <v>224.36768702792492</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-18.565560940126211</v>
+        <v>-18.461829425760769</v>
       </c>
       <c r="B81">
-        <v>6.4056761298127833</v>
+        <v>6.6793062651122153</v>
       </c>
       <c r="C81">
         <v>224.36768702792492</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-19.506737321820886</v>
+        <v>-19.442204699430402</v>
       </c>
       <c r="B82">
-        <v>7.13623848417585</v>
+        <v>7.3102241464265934</v>
       </c>
       <c r="C82">
         <v>224.36768702792492</v>
@@ -2170,10 +2170,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-22.349076521780848</v>
+        <v>-22.261260595676006</v>
       </c>
       <c r="B1">
-        <v>6.497585998077068</v>
+        <v>6.7923576076518435</v>
       </c>
       <c r="C1">
         <v>250.99764529992115</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-21.012876422063666</v>
+        <v>-20.955848859988169</v>
       </c>
       <c r="B2">
-        <v>6.4498993651416692</v>
+        <v>6.6365656729809563</v>
       </c>
       <c r="C2">
         <v>250.99764529992115</v>
@@ -2192,10 +2192,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-19.731601868339947</v>
+        <v>-19.688969372905706</v>
       </c>
       <c r="B3">
-        <v>6.2292284701816509</v>
+        <v>6.3647572222616065</v>
       </c>
       <c r="C3">
         <v>250.99764529992115</v>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-18.458946673160447</v>
+        <v>-18.428469036960582</v>
       </c>
       <c r="B4">
-        <v>5.9814114931949529</v>
+        <v>6.0737418236716243</v>
       </c>
       <c r="C4">
         <v>250.99764529992115</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-17.192337796988866</v>
+        <v>-17.172561075725117</v>
       </c>
       <c r="B5">
-        <v>5.7145520467592767</v>
+        <v>5.7688992716325931</v>
       </c>
       <c r="C5">
         <v>250.99764529992115</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-15.930726710976998</v>
+        <v>-15.920517273253672</v>
       </c>
       <c r="B6">
-        <v>5.4319524009883855</v>
+        <v>5.4524221471643539</v>
       </c>
       <c r="C6">
         <v>250.99764529992115</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-14.673515263385019</v>
+        <v>-14.671922147377426</v>
       </c>
       <c r="B7">
-        <v>5.1354963940020664</v>
+        <v>5.1255614230351734</v>
       </c>
       <c r="C7">
         <v>250.99764529992115</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-13.420352088883877</v>
+        <v>-13.426531579442562</v>
       </c>
       <c r="B8">
-        <v>4.8262906269464318</v>
+        <v>4.7890521146346261</v>
       </c>
       <c r="C8">
         <v>250.99764529992115</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-12.170687351218449</v>
+        <v>-12.183963655419998</v>
       </c>
       <c r="B9">
-        <v>4.5060667716165845</v>
+        <v>4.4440441246205511</v>
       </c>
       <c r="C9">
         <v>250.99764529992115</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-10.923927319311899</v>
+        <v>-10.943805989488274</v>
       </c>
       <c r="B10">
-        <v>4.1766947435556423</v>
+        <v>4.0917791029875712</v>
       </c>
       <c r="C10">
         <v>250.99764529992115</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-9.6795011537266262</v>
+        <v>-9.7056621040316582</v>
       </c>
       <c r="B11">
-        <v>3.8399723626497959</v>
+        <v>3.7334508018091475</v>
       </c>
       <c r="C11">
         <v>250.99764529992115</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-8.4371043886293187</v>
+        <v>-8.4693204857566471</v>
       </c>
       <c r="B12">
-        <v>3.4968585232811646</v>
+        <v>3.3696960651911541</v>
       </c>
       <c r="C12">
         <v>250.99764529992115</v>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-7.1974751609645358</v>
+        <v>-7.2352935704528862</v>
       </c>
       <c r="B13">
-        <v>3.1450285134724969</v>
+        <v>2.9989720032902834</v>
       </c>
       <c r="C13">
         <v>250.99764529992115</v>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-5.961055110765848</v>
+        <v>-6.0038879267518439</v>
       </c>
       <c r="B14">
-        <v>2.7830914180511681</v>
+        <v>2.6203555704541386</v>
       </c>
       <c r="C14">
         <v>250.99764529992115</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-4.7260572876449576</v>
+        <v>-4.7738627055691092</v>
       </c>
       <c r="B15">
-        <v>2.4166751154224313</v>
+        <v>2.2375828317431541</v>
       </c>
       <c r="C15">
         <v>250.99764529992115</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-3.4908427091981182</v>
+        <v>-3.5440798060476095</v>
       </c>
       <c r="B16">
-        <v>2.05094146891339</v>
+        <v>1.8540804881968249</v>
       </c>
       <c r="C16">
         <v>250.99764529992115</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-2.2565928553815811</v>
+        <v>-2.3153595379554335</v>
       </c>
       <c r="B17">
-        <v>1.6821694879606564</v>
+        <v>1.46737867405804</v>
       </c>
       <c r="C17">
         <v>250.99764529992115</v>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-1.0248332908870339</v>
+        <v>-1.0887611357825013</v>
       </c>
       <c r="B18">
-        <v>1.3055545105879411</v>
+        <v>1.0742881465588205</v>
       </c>
       <c r="C18">
         <v>250.99764529992115</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>0.20435454301214934</v>
+        <v>0.13565887771914209</v>
       </c>
       <c r="B19">
-        <v>0.92084004305781175</v>
+        <v>0.67463872168430483</v>
       </c>
       <c r="C19">
         <v>250.99764529992115</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>1.4312502358971817</v>
+        <v>1.3580946577319304</v>
       </c>
       <c r="B20">
-        <v>0.52890663369254776</v>
+        <v>0.2690149801079077</v>
       </c>
       <c r="C20">
         <v>250.99764529992115</v>
@@ -2390,10 +2390,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>2.6561333773492648</v>
+        <v>2.5787403594382843</v>
       </c>
       <c r="B21">
-        <v>0.1306348308144327</v>
+        <v>-0.14199849749695234</v>
       </c>
       <c r="C21">
         <v>250.99764529992115</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>3.8792337967061923</v>
+        <v>3.7977555799382738</v>
       </c>
       <c r="B22">
-        <v>-0.27325153374802036</v>
+        <v>-0.55792118117962652</v>
       </c>
       <c r="C22">
         <v>250.99764529992115</v>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>5.1005822823320646</v>
+        <v>5.0151616840025044</v>
       </c>
       <c r="B23">
-        <v>-0.68265549414135929</v>
+        <v>-0.97868874388052463</v>
       </c>
       <c r="C23">
         <v>250.99764529992115</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>6.3201598623475643</v>
+        <v>6.2309454783192191</v>
       </c>
       <c r="B24">
-        <v>-1.0976368010058983</v>
+        <v>-1.4043409092628225</v>
       </c>
       <c r="C24">
         <v>250.99764529992115</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>7.5379475648733774</v>
+        <v>7.4450937695766646</v>
       </c>
       <c r="B25">
-        <v>-1.5182552049819531</v>
+        <v>-1.8349174009896974</v>
       </c>
       <c r="C25">
         <v>250.99764529992115</v>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>8.7539182283764081</v>
+        <v>8.6575876713689883</v>
       </c>
       <c r="B26">
-        <v>-1.944596249465977</v>
+        <v>-2.2704750840271455</v>
       </c>
       <c r="C26">
         <v>250.99764529992115</v>
@@ -2456,10 +2456,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>9.9680119327085048</v>
+        <v>9.868385524914002</v>
       </c>
       <c r="B27">
-        <v>-2.3768486488789997</v>
+        <v>-2.7111393885524677</v>
       </c>
       <c r="C27">
         <v>250.99764529992115</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>11.180160568067711</v>
+        <v>11.077439978335395</v>
       </c>
       <c r="B28">
-        <v>-2.8152269103981795</v>
+        <v>-3.1570528860457747</v>
       </c>
       <c r="C28">
         <v>250.99764529992115</v>
@@ -2478,10 +2478,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>12.390296024652097</v>
+        <v>12.284703679756889</v>
       </c>
       <c r="B29">
-        <v>-3.2599455412006852</v>
+        <v>-3.6083581479871865</v>
       </c>
       <c r="C29">
         <v>250.99764529992115</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>13.598387285382037</v>
+        <v>13.490155026193373</v>
       </c>
       <c r="B30">
-        <v>-3.7111022274638779</v>
+        <v>-4.0651202186748705</v>
       </c>
       <c r="C30">
         <v>250.99764529992115</v>
@@ -2500,10 +2500,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>14.804551704067206</v>
+        <v>14.693875410224527</v>
       </c>
       <c r="B31">
-        <v>-4.1683273713659261</v>
+        <v>-4.5270940336792176</v>
       </c>
       <c r="C31">
         <v>250.99764529992115</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>16.0089437272396</v>
+        <v>15.895971973321224</v>
       </c>
       <c r="B32">
-        <v>-4.6311345540851994</v>
+        <v>-4.9939570013886643</v>
       </c>
       <c r="C32">
         <v>250.99764529992115</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>17.211717801431231</v>
+        <v>17.096551856954331</v>
       </c>
       <c r="B33">
-        <v>-5.0990373568000651</v>
+        <v>-5.4653865301916555</v>
       </c>
       <c r="C33">
         <v>250.99764529992115</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>18.412968468938161</v>
+        <v>18.295680600982177</v>
       </c>
       <c r="B34">
-        <v>-5.5717380249953372</v>
+        <v>-5.9411852865221251</v>
       </c>
       <c r="C34">
         <v>250.99764529992115</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>19.612550655112848</v>
+        <v>19.493257338812924</v>
       </c>
       <c r="B35">
-        <v>-6.0496934613816364</v>
+        <v>-6.4216569689960279</v>
       </c>
       <c r="C35">
         <v>250.99764529992115</v>
@@ -2555,10 +2555,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>20.810259381071802</v>
+        <v>20.689139602242182</v>
       </c>
       <c r="B36">
-        <v>-6.5335492329760205</v>
+        <v>-6.9072305342748006</v>
       </c>
       <c r="C36">
         <v>250.99764529992115</v>
@@ -2566,10 +2566,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>22.00588966793158</v>
+        <v>21.8831849230656</v>
       </c>
       <c r="B37">
-        <v>-7.0239509067955677</v>
+        <v>-7.3983349390199029</v>
       </c>
       <c r="C37">
         <v>250.99764529992115</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>23.199089606937164</v>
+        <v>23.075148805548309</v>
       </c>
       <c r="B38">
-        <v>-7.5220067954693457</v>
+        <v>-7.89570633397183</v>
       </c>
       <c r="C38">
         <v>250.99764529992115</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>24.388919569847445</v>
+        <v>24.264378643833684</v>
       </c>
       <c r="B39">
-        <v>-8.0306761940744753</v>
+        <v>-8.4013096461873253</v>
       </c>
       <c r="C39">
         <v>250.99764529992115</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>25.574292998549783</v>
+        <v>25.4501198045346</v>
       </c>
       <c r="B40">
-        <v>-8.553381143300081</v>
+        <v>-8.9174169968021726</v>
       </c>
       <c r="C40">
         <v>250.99764529992115</v>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>26.754123334931535</v>
+        <v>26.631617654263962</v>
       </c>
       <c r="B41">
-        <v>-9.093543683835291</v>
+        <v>-9.4463005069521717</v>
       </c>
       <c r="C41">
         <v>250.99764529992115</v>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>26.754123334931535</v>
+        <v>26.631617654263962</v>
       </c>
       <c r="B42">
-        <v>-9.093543683835291</v>
+        <v>-9.4463005069521717</v>
       </c>
       <c r="C42">
         <v>250.99764529992115</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>25.522972329854468</v>
+        <v>25.414485063919969</v>
       </c>
       <c r="B43">
-        <v>-8.7150120900716832</v>
+        <v>-9.0247094234327125</v>
       </c>
       <c r="C43">
         <v>250.99764529992115</v>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>24.2950921514217</v>
+        <v>24.199229147477894</v>
       </c>
       <c r="B44">
-        <v>-8.32617925081217</v>
+        <v>-8.5974678737260817</v>
       </c>
       <c r="C44">
         <v>250.99764529992115</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>23.069397260025479</v>
+        <v>22.985096332355909</v>
       </c>
       <c r="B45">
-        <v>-7.9304639990341732</v>
+        <v>-8.1668447849958259</v>
       </c>
       <c r="C45">
         <v>250.99764529992115</v>
@@ -2665,10 +2665,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>21.844802116058059</v>
+        <v>21.771333045972206</v>
       </c>
       <c r="B46">
-        <v>-7.53128516771512</v>
+        <v>-7.7351090844054893</v>
       </c>
       <c r="C46">
         <v>250.99764529992115</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>20.620368074623393</v>
+        <v>20.557287706655316</v>
       </c>
       <c r="B47">
-        <v>-7.1315989549538843</v>
+        <v>-7.3042226152987153</v>
       </c>
       <c r="C47">
         <v>250.99764529992115</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>19.395744069672268</v>
+        <v>19.342716696375337</v>
       </c>
       <c r="B48">
-        <v>-6.732511019335166</v>
+        <v>-6.8749188857395866</v>
       </c>
       <c r="C48">
         <v>250.99764529992115</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>18.170725929867146</v>
+        <v>18.12747838801269</v>
       </c>
       <c r="B49">
-        <v>-6.3346643845651025</v>
+        <v>-6.4476243199722756</v>
       </c>
       <c r="C49">
         <v>250.99764529992115</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>16.945109483870532</v>
+        <v>16.911431154447847</v>
       </c>
       <c r="B50">
-        <v>-5.9387020743498464</v>
+        <v>-6.0227653422409713</v>
       </c>
       <c r="C50">
         <v>250.99764529992115</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>15.718750425218534</v>
+        <v>15.694474929176732</v>
       </c>
       <c r="B51">
-        <v>-5.5450785720578626</v>
+        <v>-5.6006432421821266</v>
       </c>
       <c r="C51">
         <v>250.99764529992115</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>14.491743906941888</v>
+        <v>14.476675888157249</v>
       </c>
       <c r="B52">
-        <v>-5.1534941997069037</v>
+        <v>-5.1810587710013261</v>
       </c>
       <c r="C52">
         <v>250.99764529992115</v>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>13.26424494694494</v>
+        <v>13.258141767962778</v>
       </c>
       <c r="B53">
-        <v>-4.7634607389770389</v>
+        <v>-4.7636875452964231</v>
       </c>
       <c r="C53">
         <v>250.99764529992115</v>
@@ -2753,10 +2753,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>12.036408563132049</v>
+        <v>12.038980305166703</v>
       </c>
       <c r="B54">
-        <v>-4.3744899715483418</v>
+        <v>-4.3482051816652785</v>
       </c>
       <c r="C54">
         <v>250.99764529992115</v>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>10.808352642607304</v>
+        <v>10.819273447791808</v>
       </c>
       <c r="B55">
-        <v>-3.9862106200245755</v>
+        <v>-3.934364943297918</v>
       </c>
       <c r="C55">
         <v>250.99764529992115</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>9.5800465492737281</v>
+        <v>9.5989999896585534</v>
       </c>
       <c r="B56">
-        <v>-3.5987191707042827</v>
+        <v>-3.5222306797530845</v>
       </c>
       <c r="C56">
         <v>250.99764529992115</v>
@@ -2786,10 +2786,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>8.3514225162340541</v>
+        <v>8.3781129360367856</v>
       </c>
       <c r="B57">
-        <v>-3.2122290508096945</v>
+        <v>-3.1119438871816829</v>
       </c>
       <c r="C57">
         <v>250.99764529992115</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>7.122412776591049</v>
+        <v>7.1565652921963814</v>
       </c>
       <c r="B58">
-        <v>-2.8269536875630514</v>
+        <v>-2.7036460617346303</v>
       </c>
       <c r="C58">
         <v>250.99764529992115</v>
@@ -2808,10 +2808,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>5.8929577152496329</v>
+        <v>5.9343157170776468</v>
       </c>
       <c r="B59">
-        <v>-2.4430808346414006</v>
+        <v>-2.2974616769603582</v>
       </c>
       <c r="C59">
         <v>250.99764529992115</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>4.663030324323528</v>
+        <v>4.7113454843027842</v>
       </c>
       <c r="B60">
-        <v>-2.0606955515410776</v>
+        <v>-1.8934471159974131</v>
       </c>
       <c r="C60">
         <v>250.99764529992115</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>3.4326117477286426</v>
+        <v>3.4876415211644485</v>
       </c>
       <c r="B61">
-        <v>-1.6798572242132333</v>
+        <v>-1.4916417393818653</v>
       </c>
       <c r="C61">
         <v>250.99764529992115</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>2.2016831293808834</v>
+        <v>2.2631907549552994</v>
       </c>
       <c r="B62">
-        <v>-1.3006252386090196</v>
+        <v>-1.0920849076497856</v>
       </c>
       <c r="C62">
         <v>250.99764529992115</v>
@@ -2852,10 +2852,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>0.97027533409275324</v>
+        <v>1.0380146300693844</v>
       </c>
       <c r="B63">
-        <v>-0.92290238810598346</v>
+        <v>-0.69471205400385749</v>
       </c>
       <c r="C63">
         <v>250.99764529992115</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-0.26138188973689719</v>
+        <v>-0.18772734069371061</v>
       </c>
       <c r="B64">
-        <v>-0.54596509578724339</v>
+        <v>-0.29904290231321257</v>
       </c>
       <c r="C64">
         <v>250.99764529992115</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-1.4930090728126129</v>
+        <v>-1.4138411274330007</v>
       </c>
       <c r="B65">
-        <v>-0.16893319216231639</v>
+        <v>0.09550675088640137</v>
       </c>
       <c r="C65">
         <v>250.99764529992115</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-2.724326745838952</v>
+        <v>-2.6401327002475137</v>
       </c>
       <c r="B66">
-        <v>0.20907349225928482</v>
+        <v>0.48952110905924073</v>
       </c>
       <c r="C66">
         <v>250.99764529992115</v>
@@ -2896,10 +2896,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-3.95541650198831</v>
+        <v>-3.8666587400969639</v>
       </c>
       <c r="B67">
-        <v>0.58779798534449357</v>
+        <v>0.88282951184389979</v>
       </c>
       <c r="C67">
         <v>250.99764529992115</v>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-5.1878041843044747</v>
+        <v>-5.0944787713838506</v>
       </c>
       <c r="B68">
-        <v>0.96243474846603749</v>
+        <v>1.2722418435763399</v>
       </c>
       <c r="C68">
         <v>250.99764529992115</v>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-6.4226715966912709</v>
+        <v>-6.3244134412779731</v>
       </c>
       <c r="B69">
-        <v>1.3292617708097863</v>
+        <v>1.6552872226187017</v>
       </c>
       <c r="C69">
         <v>250.99764529992115</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-7.6583801366212292</v>
+        <v>-7.5553250445755031</v>
       </c>
       <c r="B70">
-        <v>1.6934397193083657</v>
+        <v>2.0353911587404667</v>
       </c>
       <c r="C70">
         <v>250.99764529992115</v>
@@ -2940,10 +2940,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-8.8931432680414577</v>
+        <v>-8.78597316373555</v>
       </c>
       <c r="B71">
-        <v>2.0605951674459528</v>
+        <v>2.416288417670307</v>
       </c>
       <c r="C71">
         <v>250.99764529992115</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-10.127403127228604</v>
+        <v>-10.016664884242553</v>
       </c>
       <c r="B72">
-        <v>2.429335637166163</v>
+        <v>2.7970543975662974</v>
       </c>
       <c r="C72">
         <v>250.99764529992115</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-11.361898386691063</v>
+        <v>-11.247913199692945</v>
       </c>
       <c r="B73">
-        <v>2.7973347297699696</v>
+        <v>3.176144529088015</v>
       </c>
       <c r="C73">
         <v>250.99764529992115</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-12.596325191534657</v>
+        <v>-12.479507233105792</v>
       </c>
       <c r="B74">
-        <v>3.1655494155283361</v>
+        <v>3.5541937404716437</v>
       </c>
       <c r="C74">
         <v>250.99764529992115</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-13.830113351247011</v>
+        <v>-13.711051182741649</v>
       </c>
       <c r="B75">
-        <v>3.5357754705817146</v>
+        <v>3.9323937487987921</v>
       </c>
       <c r="C75">
         <v>250.99764529992115</v>
@@ -2995,10 +2995,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-15.062669860245551</v>
+        <v>-14.942133418404438</v>
       </c>
       <c r="B76">
-        <v>3.9098805255785245</v>
+        <v>4.3119839289561721</v>
       </c>
       <c r="C76">
         <v>250.99764529992115</v>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-16.293445646812728</v>
+        <v>-16.172372822355314</v>
       </c>
       <c r="B77">
-        <v>4.2895938444548927</v>
+        <v>4.6941117860561308</v>
       </c>
       <c r="C77">
         <v>250.99764529992115</v>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-17.522090189761311</v>
+        <v>-17.401526155141031</v>
       </c>
       <c r="B78">
-        <v>4.6760193697898087</v>
+        <v>5.07950968830844</v>
       </c>
       <c r="C78">
         <v>250.99764529992115</v>
@@ -3028,10 +3028,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-18.748006217463104</v>
+        <v>-18.629178851257088</v>
       </c>
       <c r="B79">
-        <v>5.0710381678515049</v>
+        <v>5.4694258485023663</v>
       </c>
       <c r="C79">
         <v>250.99764529992115</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-19.970146152473209</v>
+        <v>-19.854603685674668</v>
       </c>
       <c r="B80">
-        <v>5.4779495123739519</v>
+        <v>5.8660498641122194</v>
       </c>
       <c r="C80">
         <v>250.99764529992115</v>
@@ -3050,10 +3050,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-21.185937961532893</v>
+        <v>-21.076014930036241</v>
       </c>
       <c r="B81">
-        <v>5.9048538467321618</v>
+        <v>6.2747583739314008</v>
       </c>
       <c r="C81">
         <v>250.99764529992115</v>
@@ -3061,10 +3061,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-22.349076521780848</v>
+        <v>-22.261260595676006</v>
       </c>
       <c r="B82">
-        <v>6.497585998077068</v>
+        <v>6.7923576076518435</v>
       </c>
       <c r="C82">
         <v>250.99764529992115</v>
